--- a/2 FINANCE/TRESORERIE/2026 1027 Modèle - Trésorerie et mois de survie.xlsx
+++ b/2 FINANCE/TRESORERIE/2026 1027 Modèle - Trésorerie et mois de survie.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vians\Documents\Claude\Projects\HEC-GEMM-Groupe-7\2 FINANCE\TRESORERIE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{36237A43-4D27-40F7-862F-AFFB3FA11D48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A87CBE3C-E37C-4301-862D-1A048EBBB96D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{2D54D8BB-BD50-4D46-AD8E-735E0D6561AC}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="103">
   <si>
     <t>Trésorerie — trésorerie disponible, consommation mensuelle, mois de survie</t>
   </si>
@@ -173,9 +173,6 @@
     <t>Suivi mensuel de la trésorerie</t>
   </si>
   <si>
-    <t>Montants constatés (pas prévus). Saisir la trésorerie de départ du premier mois, puis les flux de chaque mois.</t>
-  </si>
-  <si>
     <t>Premier mois suivi (date) :</t>
   </si>
   <si>
@@ -327,6 +324,33 @@
   </si>
   <si>
     <t>Phrase type à reprendre : « Au [date], la trésorerie disponible est de [ligne 6] € ([pièce]) ; la consommation mensuelle est de [ligne 8] € ([source]) ; soit [ligne 10] mois de survie. »</t>
+  </si>
+  <si>
+    <t>État du fichier</t>
+  </si>
+  <si>
+    <t>Mis à jour le 27/10/2026 : la société n'est pas créée, aucun relevé n'existe. L'état de départ et le suivi mensuel sont une SIMULATION (H) tirée du budget prévisionnel de 2 FINANCE/PREVISIONS (novembre 2026 à octobre 2027) et de l'apport envisagé dans 2 FINANCE/FINANCEMENT. À remplacer par les montants constatés dès l'ouverture du compte. Voir 2 FINANCE/2026 1027 Données financières manquantes et hypothèses temporaires.md.</t>
+  </si>
+  <si>
+    <t>Compte professionnel à ouvrir (apports en capital)</t>
+  </si>
+  <si>
+    <t>Aucune : société non créée, hypothèse temporaire</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>Apport envisagé (2 FINANCE/FINANCEMENT, ligne 1)</t>
+  </si>
+  <si>
+    <t>SIMULATION au 27/10/2026 : flux repris du budget prévisionnel (H), sans TVA ni délais de paiement. À remplacer par les montants constatés.</t>
+  </si>
+  <si>
+    <t>Aucune : apport envisagé, société non créée (H)</t>
+  </si>
+  <si>
+    <t>H : moyenne des mois à consommation positive de la simulation (ligne 9), à remplacer par la consommation constatée</t>
   </si>
 </sst>
 </file>
@@ -339,7 +363,7 @@
     <numFmt numFmtId="166" formatCode="#,##0\ &quot;€&quot;;\-#,##0\ &quot;€&quot;;&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="#,##0.0;\-#,##0.0;&quot;-&quot;"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -403,6 +427,14 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -498,7 +530,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -548,12 +580,6 @@
     <xf numFmtId="166" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -566,6 +592,13 @@
     <xf numFmtId="14" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -900,7 +933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D3D9264-03D7-4A56-BBF2-4B1A5EDDE9D5}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.6328125" style="1" customWidth="1"/>
@@ -1020,6 +1053,14 @@
       </c>
       <c r="B16" s="9" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="50" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1092,12 +1133,24 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
+      <c r="A6" s="12">
+        <v>46327</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" s="13">
+        <v>7000</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="12"/>
@@ -1358,75 +1411,77 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="13" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>43</v>
+      <c r="A2" s="33" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="14"/>
+        <v>43</v>
+      </c>
+      <c r="C3" s="14">
+        <v>46327</v>
+      </c>
     </row>
     <row r="5" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="15" t="str">
+      <c r="C5" s="15">
         <f t="shared" ref="C5:N5" si="0">IF($C$3="","Mois "&amp;(COLUMN()-2),EDATE($C$3,COLUMN()-3))</f>
-        <v>Mois 1</v>
-      </c>
-      <c r="D5" s="15" t="str">
+        <v>46327</v>
+      </c>
+      <c r="D5" s="15">
         <f t="shared" si="0"/>
-        <v>Mois 2</v>
-      </c>
-      <c r="E5" s="15" t="str">
+        <v>46357</v>
+      </c>
+      <c r="E5" s="15">
         <f t="shared" si="0"/>
-        <v>Mois 3</v>
-      </c>
-      <c r="F5" s="15" t="str">
+        <v>46388</v>
+      </c>
+      <c r="F5" s="15">
         <f t="shared" si="0"/>
-        <v>Mois 4</v>
-      </c>
-      <c r="G5" s="15" t="str">
+        <v>46419</v>
+      </c>
+      <c r="G5" s="15">
         <f t="shared" si="0"/>
-        <v>Mois 5</v>
-      </c>
-      <c r="H5" s="15" t="str">
+        <v>46447</v>
+      </c>
+      <c r="H5" s="15">
         <f t="shared" si="0"/>
-        <v>Mois 6</v>
-      </c>
-      <c r="I5" s="15" t="str">
+        <v>46478</v>
+      </c>
+      <c r="I5" s="15">
         <f t="shared" si="0"/>
-        <v>Mois 7</v>
-      </c>
-      <c r="J5" s="15" t="str">
+        <v>46508</v>
+      </c>
+      <c r="J5" s="15">
         <f t="shared" si="0"/>
-        <v>Mois 8</v>
-      </c>
-      <c r="K5" s="15" t="str">
+        <v>46539</v>
+      </c>
+      <c r="K5" s="15">
         <f t="shared" si="0"/>
-        <v>Mois 9</v>
-      </c>
-      <c r="L5" s="15" t="str">
+        <v>46569</v>
+      </c>
+      <c r="L5" s="15">
         <f t="shared" si="0"/>
-        <v>Mois 10</v>
-      </c>
-      <c r="M5" s="15" t="str">
+        <v>46600</v>
+      </c>
+      <c r="M5" s="15">
         <f t="shared" si="0"/>
-        <v>Mois 11</v>
-      </c>
-      <c r="N5" s="15" t="str">
+        <v>46631</v>
+      </c>
+      <c r="N5" s="15">
         <f t="shared" si="0"/>
-        <v>Mois 12</v>
+        <v>46661</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
@@ -1444,61 +1499,63 @@
     </row>
     <row r="7" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" s="23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B7" s="18">
         <f>C7</f>
         <v>0</v>
       </c>
-      <c r="C7" s="17"/>
+      <c r="C7" s="17">
+        <v>0</v>
+      </c>
       <c r="D7" s="18">
         <f t="shared" ref="D7:N7" si="1">IF(C30&lt;&gt;"",C30,C29)</f>
-        <v>0</v>
+        <v>4638</v>
       </c>
       <c r="E7" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2828</v>
       </c>
       <c r="F7" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>163.93000000000029</v>
       </c>
       <c r="G7" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-3998.3600000000006</v>
       </c>
       <c r="H7" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-5471.6100000000006</v>
       </c>
       <c r="I7" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-5703.5400000000009</v>
       </c>
       <c r="J7" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-7433.68</v>
       </c>
       <c r="K7" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-7674.7900000000009</v>
       </c>
       <c r="L7" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-9138.86</v>
       </c>
       <c r="M7" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-9748.86</v>
       </c>
       <c r="N7" s="18">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-10246.86</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
@@ -1516,190 +1573,334 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B9" s="18">
-        <f>SUM(C9:N9)</f>
-        <v>0</v>
-      </c>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
+        <f t="shared" ref="B9:B15" si="2">SUM(C9:N9)</f>
+        <v>121955.34999999998</v>
+      </c>
+      <c r="C9" s="17">
+        <v>0</v>
+      </c>
+      <c r="D9" s="17">
+        <v>0</v>
+      </c>
+      <c r="E9" s="17">
+        <v>4919.6400000000003</v>
+      </c>
+      <c r="F9" s="17">
+        <v>9857.14</v>
+      </c>
+      <c r="G9" s="17">
+        <v>7125</v>
+      </c>
+      <c r="H9" s="17">
+        <v>12955.36</v>
+      </c>
+      <c r="I9" s="17">
+        <v>17892.86</v>
+      </c>
+      <c r="J9" s="17">
+        <v>15160.71</v>
+      </c>
+      <c r="K9" s="17">
+        <v>4919.6400000000003</v>
+      </c>
+      <c r="L9" s="17">
+        <v>0</v>
+      </c>
+      <c r="M9" s="17">
+        <v>25928.57</v>
+      </c>
+      <c r="N9" s="17">
+        <v>23196.43</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B10" s="18">
-        <f>SUM(C10:N10)</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C10" s="17">
+        <v>0</v>
+      </c>
+      <c r="D10" s="17">
+        <v>0</v>
+      </c>
+      <c r="E10" s="17">
+        <v>0</v>
+      </c>
+      <c r="F10" s="17">
+        <v>0</v>
+      </c>
+      <c r="G10" s="17">
+        <v>0</v>
+      </c>
+      <c r="H10" s="17">
+        <v>0</v>
+      </c>
+      <c r="I10" s="17">
+        <v>0</v>
+      </c>
+      <c r="J10" s="17">
+        <v>0</v>
+      </c>
+      <c r="K10" s="17">
+        <v>0</v>
+      </c>
+      <c r="L10" s="17">
+        <v>0</v>
+      </c>
+      <c r="M10" s="17">
+        <v>0</v>
+      </c>
+      <c r="N10" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B11" s="18">
-        <f>SUM(C11:N11)</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
+        <f t="shared" si="2"/>
+        <v>7000</v>
+      </c>
+      <c r="C11" s="17">
+        <v>7000</v>
+      </c>
+      <c r="D11" s="17">
+        <v>0</v>
+      </c>
+      <c r="E11" s="17">
+        <v>0</v>
+      </c>
+      <c r="F11" s="17">
+        <v>0</v>
+      </c>
+      <c r="G11" s="17">
+        <v>0</v>
+      </c>
+      <c r="H11" s="17">
+        <v>0</v>
+      </c>
+      <c r="I11" s="17">
+        <v>0</v>
+      </c>
+      <c r="J11" s="17">
+        <v>0</v>
+      </c>
+      <c r="K11" s="17">
+        <v>0</v>
+      </c>
+      <c r="L11" s="17">
+        <v>0</v>
+      </c>
+      <c r="M11" s="17">
+        <v>0</v>
+      </c>
+      <c r="N11" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B12" s="18">
-        <f>SUM(C12:N12)</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C12" s="17">
+        <v>0</v>
+      </c>
+      <c r="D12" s="17">
+        <v>0</v>
+      </c>
+      <c r="E12" s="17">
+        <v>0</v>
+      </c>
+      <c r="F12" s="17">
+        <v>0</v>
+      </c>
+      <c r="G12" s="17">
+        <v>0</v>
+      </c>
+      <c r="H12" s="17">
+        <v>0</v>
+      </c>
+      <c r="I12" s="17">
+        <v>0</v>
+      </c>
+      <c r="J12" s="17">
+        <v>0</v>
+      </c>
+      <c r="K12" s="17">
+        <v>0</v>
+      </c>
+      <c r="L12" s="17">
+        <v>0</v>
+      </c>
+      <c r="M12" s="17">
+        <v>0</v>
+      </c>
+      <c r="N12" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="18">
-        <f>SUM(C13:N13)</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C13" s="17">
+        <v>0</v>
+      </c>
+      <c r="D13" s="17">
+        <v>0</v>
+      </c>
+      <c r="E13" s="17">
+        <v>0</v>
+      </c>
+      <c r="F13" s="17">
+        <v>0</v>
+      </c>
+      <c r="G13" s="17">
+        <v>0</v>
+      </c>
+      <c r="H13" s="17">
+        <v>0</v>
+      </c>
+      <c r="I13" s="17">
+        <v>0</v>
+      </c>
+      <c r="J13" s="17">
+        <v>0</v>
+      </c>
+      <c r="K13" s="17">
+        <v>0</v>
+      </c>
+      <c r="L13" s="17">
+        <v>0</v>
+      </c>
+      <c r="M13" s="17">
+        <v>0</v>
+      </c>
+      <c r="N13" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B14" s="18">
-        <f>SUM(C14:N14)</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C14" s="17">
+        <v>0</v>
+      </c>
+      <c r="D14" s="17">
+        <v>0</v>
+      </c>
+      <c r="E14" s="17">
+        <v>0</v>
+      </c>
+      <c r="F14" s="17">
+        <v>0</v>
+      </c>
+      <c r="G14" s="17">
+        <v>0</v>
+      </c>
+      <c r="H14" s="17">
+        <v>0</v>
+      </c>
+      <c r="I14" s="17">
+        <v>0</v>
+      </c>
+      <c r="J14" s="17">
+        <v>0</v>
+      </c>
+      <c r="K14" s="17">
+        <v>0</v>
+      </c>
+      <c r="L14" s="17">
+        <v>0</v>
+      </c>
+      <c r="M14" s="17">
+        <v>0</v>
+      </c>
+      <c r="N14" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A15" s="23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B15" s="19">
-        <f>SUM(C15:N15)</f>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>128955.34999999998</v>
       </c>
       <c r="C15" s="19">
-        <f t="shared" ref="C15:N15" si="2">SUM(C9:C14)</f>
-        <v>0</v>
+        <f t="shared" ref="C15:N15" si="3">SUM(C9:C14)</f>
+        <v>7000</v>
       </c>
       <c r="D15" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E15" s="19">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>4919.6400000000003</v>
       </c>
       <c r="F15" s="19">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>9857.14</v>
       </c>
       <c r="G15" s="19">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>7125</v>
       </c>
       <c r="H15" s="19">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>12955.36</v>
       </c>
       <c r="I15" s="19">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>17892.86</v>
       </c>
       <c r="J15" s="19">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>15160.71</v>
       </c>
       <c r="K15" s="19">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>4919.6400000000003</v>
       </c>
       <c r="L15" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M15" s="19">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>25928.57</v>
       </c>
       <c r="N15" s="19">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>23196.43</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A16" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -1717,253 +1918,469 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B17" s="18">
-        <f>SUM(C17:N17)</f>
-        <v>0</v>
-      </c>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17"/>
-      <c r="N17" s="17"/>
+        <f t="shared" ref="B17:B26" si="4">SUM(C17:N17)</f>
+        <v>30500</v>
+      </c>
+      <c r="C17" s="17">
+        <v>0</v>
+      </c>
+      <c r="D17" s="17">
+        <v>0</v>
+      </c>
+      <c r="E17" s="17">
+        <v>1500</v>
+      </c>
+      <c r="F17" s="17">
+        <v>2500</v>
+      </c>
+      <c r="G17" s="17">
+        <v>1500</v>
+      </c>
+      <c r="H17" s="17">
+        <v>3500</v>
+      </c>
+      <c r="I17" s="17">
+        <v>4500</v>
+      </c>
+      <c r="J17" s="17">
+        <v>3500</v>
+      </c>
+      <c r="K17" s="17">
+        <v>1500</v>
+      </c>
+      <c r="L17" s="17">
+        <v>0</v>
+      </c>
+      <c r="M17" s="17">
+        <v>6500</v>
+      </c>
+      <c r="N17" s="17">
+        <v>5500</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B18" s="18">
-        <f>SUM(C18:N18)</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
-      <c r="N18" s="17"/>
+        <f t="shared" si="4"/>
+        <v>32550</v>
+      </c>
+      <c r="C18" s="17">
+        <v>0</v>
+      </c>
+      <c r="D18" s="17">
+        <v>0</v>
+      </c>
+      <c r="E18" s="17">
+        <v>950</v>
+      </c>
+      <c r="F18" s="17">
+        <v>3700</v>
+      </c>
+      <c r="G18" s="17">
+        <v>2000</v>
+      </c>
+      <c r="H18" s="17">
+        <v>2750</v>
+      </c>
+      <c r="I18" s="17">
+        <v>5500</v>
+      </c>
+      <c r="J18" s="17">
+        <v>3800</v>
+      </c>
+      <c r="K18" s="17">
+        <v>950</v>
+      </c>
+      <c r="L18" s="17">
+        <v>0</v>
+      </c>
+      <c r="M18" s="17">
+        <v>7300</v>
+      </c>
+      <c r="N18" s="17">
+        <v>5600</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B19" s="18">
-        <f>SUM(C19:N19)</f>
-        <v>0</v>
-      </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17"/>
+        <f t="shared" si="4"/>
+        <v>41347</v>
+      </c>
+      <c r="C19" s="17">
+        <v>0</v>
+      </c>
+      <c r="D19" s="17">
+        <v>0</v>
+      </c>
+      <c r="E19" s="17">
+        <v>2485</v>
+      </c>
+      <c r="F19" s="17">
+        <v>4006</v>
+      </c>
+      <c r="G19" s="17">
+        <v>3208</v>
+      </c>
+      <c r="H19" s="17">
+        <v>4235</v>
+      </c>
+      <c r="I19" s="17">
+        <v>5756</v>
+      </c>
+      <c r="J19" s="17">
+        <v>4958</v>
+      </c>
+      <c r="K19" s="17">
+        <v>2485</v>
+      </c>
+      <c r="L19" s="17">
+        <v>0</v>
+      </c>
+      <c r="M19" s="17">
+        <v>7506</v>
+      </c>
+      <c r="N19" s="17">
+        <v>6708</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B20" s="18">
-        <f>SUM(C20:N20)</f>
-        <v>0</v>
-      </c>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="17"/>
-      <c r="N20" s="17"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="C20" s="17">
+        <v>0</v>
+      </c>
+      <c r="D20" s="17">
+        <v>0</v>
+      </c>
+      <c r="E20" s="17">
+        <v>0</v>
+      </c>
+      <c r="F20" s="17">
+        <v>0</v>
+      </c>
+      <c r="G20" s="17">
+        <v>0</v>
+      </c>
+      <c r="H20" s="17">
+        <v>0</v>
+      </c>
+      <c r="I20" s="17">
+        <v>0</v>
+      </c>
+      <c r="J20" s="17">
+        <v>0</v>
+      </c>
+      <c r="K20" s="17">
+        <v>0</v>
+      </c>
+      <c r="L20" s="17">
+        <v>0</v>
+      </c>
+      <c r="M20" s="17">
+        <v>0</v>
+      </c>
+      <c r="N20" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B21" s="18">
-        <f>SUM(C21:N21)</f>
-        <v>0</v>
-      </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
-      <c r="N21" s="17"/>
+        <f t="shared" si="4"/>
+        <v>4872</v>
+      </c>
+      <c r="C21" s="17">
+        <v>2012</v>
+      </c>
+      <c r="D21" s="17">
+        <v>260</v>
+      </c>
+      <c r="E21" s="17">
+        <v>260</v>
+      </c>
+      <c r="F21" s="17">
+        <v>260</v>
+      </c>
+      <c r="G21" s="17">
+        <v>260</v>
+      </c>
+      <c r="H21" s="17">
+        <v>260</v>
+      </c>
+      <c r="I21" s="17">
+        <v>260</v>
+      </c>
+      <c r="J21" s="17">
+        <v>260</v>
+      </c>
+      <c r="K21" s="17">
+        <v>260</v>
+      </c>
+      <c r="L21" s="17">
+        <v>260</v>
+      </c>
+      <c r="M21" s="17">
+        <v>260</v>
+      </c>
+      <c r="N21" s="17">
+        <v>260</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B22" s="18">
-        <f>SUM(C22:N22)</f>
-        <v>0</v>
-      </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" s="17"/>
+        <f t="shared" si="4"/>
+        <v>7200</v>
+      </c>
+      <c r="C22" s="17">
+        <v>300</v>
+      </c>
+      <c r="D22" s="17">
+        <v>1500</v>
+      </c>
+      <c r="E22" s="17">
+        <v>1500</v>
+      </c>
+      <c r="F22" s="17">
+        <v>1500</v>
+      </c>
+      <c r="G22" s="17">
+        <v>300</v>
+      </c>
+      <c r="H22" s="17">
+        <v>300</v>
+      </c>
+      <c r="I22" s="17">
+        <v>300</v>
+      </c>
+      <c r="J22" s="17">
+        <v>300</v>
+      </c>
+      <c r="K22" s="17">
+        <v>300</v>
+      </c>
+      <c r="L22" s="17">
+        <v>300</v>
+      </c>
+      <c r="M22" s="17">
+        <v>300</v>
+      </c>
+      <c r="N22" s="17">
+        <v>300</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B23" s="18">
-        <f>SUM(C23:N23)</f>
-        <v>0</v>
-      </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="17"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="C23" s="17">
+        <v>0</v>
+      </c>
+      <c r="D23" s="17">
+        <v>0</v>
+      </c>
+      <c r="E23" s="17">
+        <v>0</v>
+      </c>
+      <c r="F23" s="17">
+        <v>0</v>
+      </c>
+      <c r="G23" s="17">
+        <v>0</v>
+      </c>
+      <c r="H23" s="17">
+        <v>0</v>
+      </c>
+      <c r="I23" s="17">
+        <v>0</v>
+      </c>
+      <c r="J23" s="17">
+        <v>0</v>
+      </c>
+      <c r="K23" s="17">
+        <v>0</v>
+      </c>
+      <c r="L23" s="17">
+        <v>0</v>
+      </c>
+      <c r="M23" s="17">
+        <v>0</v>
+      </c>
+      <c r="N23" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B24" s="18">
-        <f>SUM(C24:N24)</f>
-        <v>0</v>
-      </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" s="17"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="C24" s="17">
+        <v>0</v>
+      </c>
+      <c r="D24" s="17">
+        <v>0</v>
+      </c>
+      <c r="E24" s="17">
+        <v>0</v>
+      </c>
+      <c r="F24" s="17">
+        <v>0</v>
+      </c>
+      <c r="G24" s="17">
+        <v>0</v>
+      </c>
+      <c r="H24" s="17">
+        <v>0</v>
+      </c>
+      <c r="I24" s="17">
+        <v>0</v>
+      </c>
+      <c r="J24" s="17">
+        <v>0</v>
+      </c>
+      <c r="K24" s="17">
+        <v>0</v>
+      </c>
+      <c r="L24" s="17">
+        <v>0</v>
+      </c>
+      <c r="M24" s="17">
+        <v>0</v>
+      </c>
+      <c r="N24" s="17">
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B25" s="18">
-        <f>SUM(C25:N25)</f>
-        <v>0</v>
-      </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17"/>
+        <f t="shared" si="4"/>
+        <v>21742.17</v>
+      </c>
+      <c r="C25" s="17">
+        <v>50</v>
+      </c>
+      <c r="D25" s="17">
+        <v>50</v>
+      </c>
+      <c r="E25" s="17">
+        <v>888.71</v>
+      </c>
+      <c r="F25" s="17">
+        <v>2053.4299999999998</v>
+      </c>
+      <c r="G25" s="17">
+        <v>1330.25</v>
+      </c>
+      <c r="H25" s="17">
+        <v>2142.29</v>
+      </c>
+      <c r="I25" s="17">
+        <v>3307</v>
+      </c>
+      <c r="J25" s="17">
+        <v>2583.8200000000002</v>
+      </c>
+      <c r="K25" s="17">
+        <v>888.71</v>
+      </c>
+      <c r="L25" s="17">
+        <v>50</v>
+      </c>
+      <c r="M25" s="17">
+        <v>4560.57</v>
+      </c>
+      <c r="N25" s="17">
+        <v>3837.39</v>
+      </c>
     </row>
     <row r="26" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A26" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B26" s="19">
-        <f>SUM(C26:N26)</f>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>138211.16999999998</v>
       </c>
       <c r="C26" s="19">
-        <f t="shared" ref="C26:N26" si="3">SUM(C17:C25)</f>
-        <v>0</v>
+        <f t="shared" ref="C26:N26" si="5">SUM(C17:C25)</f>
+        <v>2362</v>
       </c>
       <c r="D26" s="19">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>1810</v>
       </c>
       <c r="E26" s="19">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>7583.71</v>
       </c>
       <c r="F26" s="19">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>14019.43</v>
       </c>
       <c r="G26" s="19">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>8598.25</v>
       </c>
       <c r="H26" s="19">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>13187.29</v>
       </c>
       <c r="I26" s="19">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>19623</v>
       </c>
       <c r="J26" s="19">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>15401.82</v>
       </c>
       <c r="K26" s="19">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>6383.71</v>
       </c>
       <c r="L26" s="19">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>610</v>
       </c>
       <c r="M26" s="19">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>26426.57</v>
       </c>
       <c r="N26" s="19">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>22205.39</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A27" s="22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -1981,121 +2398,121 @@
     </row>
     <row r="28" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A28" s="23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B28" s="19">
         <f>SUM(C28:N28)</f>
-        <v>0</v>
+        <v>-9255.82</v>
       </c>
       <c r="C28" s="19">
-        <f t="shared" ref="C28:N28" si="4">C15-C26</f>
-        <v>0</v>
+        <f t="shared" ref="C28:N28" si="6">C15-C26</f>
+        <v>4638</v>
       </c>
       <c r="D28" s="19">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>-1810</v>
       </c>
       <c r="E28" s="19">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>-2664.0699999999997</v>
       </c>
       <c r="F28" s="19">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>-4162.2900000000009</v>
       </c>
       <c r="G28" s="19">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>-1473.25</v>
       </c>
       <c r="H28" s="19">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>-231.93000000000029</v>
       </c>
       <c r="I28" s="19">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>-1730.1399999999994</v>
       </c>
       <c r="J28" s="19">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>-241.11000000000058</v>
       </c>
       <c r="K28" s="19">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>-1464.0699999999997</v>
       </c>
       <c r="L28" s="19">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>-610</v>
       </c>
       <c r="M28" s="19">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>-498</v>
       </c>
       <c r="N28" s="19">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>991.04000000000087</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A29" s="23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B29" s="19">
         <f>N29</f>
-        <v>0</v>
+        <v>-9255.82</v>
       </c>
       <c r="C29" s="19">
-        <f t="shared" ref="C29:N29" si="5">C7+C28</f>
-        <v>0</v>
+        <f t="shared" ref="C29:N29" si="7">C7+C28</f>
+        <v>4638</v>
       </c>
       <c r="D29" s="19">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>2828</v>
       </c>
       <c r="E29" s="19">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>163.93000000000029</v>
       </c>
       <c r="F29" s="19">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>-3998.3600000000006</v>
       </c>
       <c r="G29" s="19">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>-5471.6100000000006</v>
       </c>
       <c r="H29" s="19">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>-5703.5400000000009</v>
       </c>
       <c r="I29" s="19">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>-7433.68</v>
       </c>
       <c r="J29" s="19">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>-7674.7900000000009</v>
       </c>
       <c r="K29" s="19">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>-9138.86</v>
       </c>
       <c r="L29" s="19">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>-9748.86</v>
       </c>
       <c r="M29" s="19">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>-10246.86</v>
       </c>
       <c r="N29" s="19">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>-9255.82</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
@@ -2112,61 +2529,61 @@
     </row>
     <row r="31" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A31" s="23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="19">
-        <f t="shared" ref="C31:N31" si="6">IF(C30="",0,C29-C30)</f>
+        <f t="shared" ref="C31:N31" si="8">IF(C30="",0,C29-C30)</f>
         <v>0</v>
       </c>
       <c r="D31" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E31" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F31" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G31" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H31" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I31" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J31" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K31" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L31" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M31" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="N31" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C32" s="20"/>
       <c r="D32" s="20"/>
@@ -2183,7 +2600,7 @@
     </row>
     <row r="33" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A33" s="22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
@@ -2201,118 +2618,118 @@
     </row>
     <row r="34" spans="1:14" ht="26" x14ac:dyDescent="0.3">
       <c r="A34" s="23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B34" s="19">
         <f>SUM(C34:N34)</f>
-        <v>0</v>
+        <v>16255.82</v>
       </c>
       <c r="C34" s="19">
-        <f t="shared" ref="C34:N34" si="7">C26-C9-C10-C14</f>
-        <v>0</v>
+        <f t="shared" ref="C34:N34" si="9">C26-C9-C10-C14</f>
+        <v>2362</v>
       </c>
       <c r="D34" s="19">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>1810</v>
       </c>
       <c r="E34" s="19">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>2664.0699999999997</v>
       </c>
       <c r="F34" s="19">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>4162.2900000000009</v>
       </c>
       <c r="G34" s="19">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>1473.25</v>
       </c>
       <c r="H34" s="19">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>231.93000000000029</v>
       </c>
       <c r="I34" s="19">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>1730.1399999999994</v>
       </c>
       <c r="J34" s="19">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>241.11000000000058</v>
       </c>
       <c r="K34" s="19">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>1464.0699999999997</v>
       </c>
       <c r="L34" s="19">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>610</v>
       </c>
       <c r="M34" s="19">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>498</v>
       </c>
       <c r="N34" s="19">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>-991.04000000000087</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A35" s="23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="21">
-        <f t="shared" ref="C35:N35" si="8">IF(C34&gt;0,IF(C30&lt;&gt;"",C30,C29)/C34,0)</f>
-        <v>0</v>
+        <f t="shared" ref="C35:N35" si="10">IF(C34&gt;0,IF(C30&lt;&gt;"",C30,C29)/C34,0)</f>
+        <v>1.9635901778154106</v>
       </c>
       <c r="D35" s="21">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>1.5624309392265194</v>
       </c>
       <c r="E35" s="21">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>6.1533668409613974E-2</v>
       </c>
       <c r="F35" s="21">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>-0.96061543044814268</v>
       </c>
       <c r="G35" s="21">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>-3.7139725097573395</v>
       </c>
       <c r="H35" s="21">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>-24.591644030526425</v>
       </c>
       <c r="I35" s="21">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>-4.296577155605906</v>
       </c>
       <c r="J35" s="21">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>-31.831072954253173</v>
       </c>
       <c r="K35" s="21">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>-6.2420922496875164</v>
       </c>
       <c r="L35" s="21">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>-15.981737704918034</v>
       </c>
       <c r="M35" s="21">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>-20.576024096385542</v>
       </c>
       <c r="N35" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2333,102 +2750,108 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="13" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="26" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="B4" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C4" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B5" s="25">
         <f>IF(COUNT('États de trésorerie'!A6:A35)=0,0,MAX('États de trésorerie'!A6:A35))</f>
-        <v>0</v>
+        <v>46327</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B6" s="26">
         <f>IF(B5=0,0,SUMIFS('États de trésorerie'!C6:C35,'États de trésorerie'!A6:A35,B5))</f>
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="32"/>
+    </row>
+    <row r="8" spans="1:3" ht="25" x14ac:dyDescent="0.25">
+      <c r="A8" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="B7" s="27"/>
-      <c r="C7" s="28"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="30"/>
+      <c r="B8" s="27">
+        <v>1568</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="9" spans="1:3" ht="25" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B9" s="26">
         <f>IFERROR(AVERAGEIF('Suivi mensuel'!C34:N34,"&gt;0"),0)</f>
-        <v>0</v>
+        <v>1567.8963636363637</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="29">
         <f>IF(B8&gt;0,B6/B8,0)</f>
-        <v>0</v>
+        <v>4.4642857142857144</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="30">
+        <f>IF(AND(B10&gt;0,B5&gt;0),EDATE(B5,INT(B10)),"")</f>
+        <v>46447</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>92</v>
-      </c>
-      <c r="B11" s="32" t="str">
-        <f>IF(AND(B10&gt;0,B5&gt;0),EDATE(B5,INT(B10)),"")</f>
-        <v/>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/2 FINANCE/TRESORERIE/2026 1027 Modèle - Trésorerie et mois de survie.xlsx
+++ b/2 FINANCE/TRESORERIE/2026 1027 Modèle - Trésorerie et mois de survie.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vians\Documents\Claude\Projects\HEC-GEMM-Groupe-7\2 FINANCE\TRESORERIE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A87CBE3C-E37C-4301-862D-1A048EBBB96D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DE7D47A-DECD-4C97-8966-7DA43DBA166E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{2D54D8BB-BD50-4D46-AD8E-735E0D6561AC}"/>
   </bookViews>
@@ -344,13 +344,13 @@
     <t>Apport envisagé (2 FINANCE/FINANCEMENT, ligne 1)</t>
   </si>
   <si>
-    <t>SIMULATION au 27/10/2026 : flux repris du budget prévisionnel (H), sans TVA ni délais de paiement. À remplacer par les montants constatés.</t>
-  </si>
-  <si>
     <t>Aucune : apport envisagé, société non créée (H)</t>
   </si>
   <si>
     <t>H : moyenne des mois à consommation positive de la simulation (ligne 9), à remplacer par la consommation constatée</t>
+  </si>
+  <si>
+    <t>SIMULATION mise à jour le 28/10/2026 : flux repris du budget prévisionnel (H), y compris le staffing des Opérations et les investissements de l'année 1 (en novembre, dans « Autres décaissements »), sans TVA ni délais de paiement. À remplacer par les montants constatés.</t>
   </si>
 </sst>
 </file>
@@ -592,13 +592,13 @@
     <xf numFmtId="14" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1411,8 +1411,8 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="13" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
-        <v>100</v>
+      <c r="A2" s="31" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -1510,47 +1510,47 @@
       </c>
       <c r="D7" s="18">
         <f t="shared" ref="D7:N7" si="1">IF(C30&lt;&gt;"",C30,C29)</f>
-        <v>4638</v>
+        <v>1638</v>
       </c>
       <c r="E7" s="18">
         <f t="shared" si="1"/>
-        <v>2828</v>
+        <v>-172</v>
       </c>
       <c r="F7" s="18">
         <f t="shared" si="1"/>
-        <v>163.93000000000029</v>
+        <v>-5602.0699999999988</v>
       </c>
       <c r="G7" s="18">
         <f t="shared" si="1"/>
-        <v>-3998.3600000000006</v>
+        <v>-11490.36</v>
       </c>
       <c r="H7" s="18">
         <f t="shared" si="1"/>
-        <v>-5471.6100000000006</v>
+        <v>-15519.61</v>
       </c>
       <c r="I7" s="18">
         <f t="shared" si="1"/>
-        <v>-5703.5400000000009</v>
+        <v>-19607.54</v>
       </c>
       <c r="J7" s="18">
         <f t="shared" si="1"/>
-        <v>-7433.68</v>
+        <v>-24153.68</v>
       </c>
       <c r="K7" s="18">
         <f t="shared" si="1"/>
-        <v>-7674.7900000000009</v>
+        <v>-28040.79</v>
       </c>
       <c r="L7" s="18">
         <f t="shared" si="1"/>
-        <v>-9138.86</v>
+        <v>-32270.86</v>
       </c>
       <c r="M7" s="18">
         <f t="shared" si="1"/>
-        <v>-9748.86</v>
+        <v>-32880.86</v>
       </c>
       <c r="N7" s="18">
         <f t="shared" si="1"/>
-        <v>-10246.86</v>
+        <v>-37284.86</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="B19" s="18">
         <f t="shared" si="4"/>
-        <v>41347</v>
+        <v>70121</v>
       </c>
       <c r="C19" s="17">
         <v>0</v>
@@ -2021,34 +2021,34 @@
         <v>0</v>
       </c>
       <c r="E19" s="17">
-        <v>2485</v>
+        <v>5251</v>
       </c>
       <c r="F19" s="17">
-        <v>4006</v>
+        <v>5732</v>
       </c>
       <c r="G19" s="17">
-        <v>3208</v>
+        <v>5764</v>
       </c>
       <c r="H19" s="17">
-        <v>4235</v>
+        <v>8091</v>
       </c>
       <c r="I19" s="17">
-        <v>5756</v>
+        <v>8572</v>
       </c>
       <c r="J19" s="17">
-        <v>4958</v>
+        <v>8604</v>
       </c>
       <c r="K19" s="17">
-        <v>2485</v>
+        <v>5251</v>
       </c>
       <c r="L19" s="17">
         <v>0</v>
       </c>
       <c r="M19" s="17">
-        <v>7506</v>
+        <v>11412</v>
       </c>
       <c r="N19" s="17">
-        <v>6708</v>
+        <v>11444</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -2282,10 +2282,10 @@
       </c>
       <c r="B25" s="18">
         <f t="shared" si="4"/>
-        <v>21742.17</v>
+        <v>24742.17</v>
       </c>
       <c r="C25" s="17">
-        <v>50</v>
+        <v>3050</v>
       </c>
       <c r="D25" s="17">
         <v>50</v>
@@ -2327,11 +2327,11 @@
       </c>
       <c r="B26" s="19">
         <f t="shared" si="4"/>
-        <v>138211.16999999998</v>
+        <v>169985.16999999998</v>
       </c>
       <c r="C26" s="19">
         <f t="shared" ref="C26:N26" si="5">SUM(C17:C25)</f>
-        <v>2362</v>
+        <v>5362</v>
       </c>
       <c r="D26" s="19">
         <f t="shared" si="5"/>
@@ -2339,31 +2339,31 @@
       </c>
       <c r="E26" s="19">
         <f t="shared" si="5"/>
-        <v>7583.71</v>
+        <v>10349.709999999999</v>
       </c>
       <c r="F26" s="19">
         <f t="shared" si="5"/>
-        <v>14019.43</v>
+        <v>15745.43</v>
       </c>
       <c r="G26" s="19">
         <f t="shared" si="5"/>
-        <v>8598.25</v>
+        <v>11154.25</v>
       </c>
       <c r="H26" s="19">
         <f t="shared" si="5"/>
-        <v>13187.29</v>
+        <v>17043.29</v>
       </c>
       <c r="I26" s="19">
         <f t="shared" si="5"/>
-        <v>19623</v>
+        <v>22439</v>
       </c>
       <c r="J26" s="19">
         <f t="shared" si="5"/>
-        <v>15401.82</v>
+        <v>19047.82</v>
       </c>
       <c r="K26" s="19">
         <f t="shared" si="5"/>
-        <v>6383.71</v>
+        <v>9149.7099999999991</v>
       </c>
       <c r="L26" s="19">
         <f t="shared" si="5"/>
@@ -2371,11 +2371,11 @@
       </c>
       <c r="M26" s="19">
         <f t="shared" si="5"/>
-        <v>26426.57</v>
+        <v>30332.57</v>
       </c>
       <c r="N26" s="19">
         <f t="shared" si="5"/>
-        <v>22205.39</v>
+        <v>26941.39</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -2402,11 +2402,11 @@
       </c>
       <c r="B28" s="19">
         <f>SUM(C28:N28)</f>
-        <v>-9255.82</v>
+        <v>-41029.82</v>
       </c>
       <c r="C28" s="19">
         <f t="shared" ref="C28:N28" si="6">C15-C26</f>
-        <v>4638</v>
+        <v>1638</v>
       </c>
       <c r="D28" s="19">
         <f t="shared" si="6"/>
@@ -2414,31 +2414,31 @@
       </c>
       <c r="E28" s="19">
         <f t="shared" si="6"/>
-        <v>-2664.0699999999997</v>
+        <v>-5430.0699999999988</v>
       </c>
       <c r="F28" s="19">
         <f t="shared" si="6"/>
-        <v>-4162.2900000000009</v>
+        <v>-5888.2900000000009</v>
       </c>
       <c r="G28" s="19">
         <f t="shared" si="6"/>
-        <v>-1473.25</v>
+        <v>-4029.25</v>
       </c>
       <c r="H28" s="19">
         <f t="shared" si="6"/>
-        <v>-231.93000000000029</v>
+        <v>-4087.9300000000003</v>
       </c>
       <c r="I28" s="19">
         <f t="shared" si="6"/>
-        <v>-1730.1399999999994</v>
+        <v>-4546.1399999999994</v>
       </c>
       <c r="J28" s="19">
         <f t="shared" si="6"/>
-        <v>-241.11000000000058</v>
+        <v>-3887.1100000000006</v>
       </c>
       <c r="K28" s="19">
         <f t="shared" si="6"/>
-        <v>-1464.0699999999997</v>
+        <v>-4230.0699999999988</v>
       </c>
       <c r="L28" s="19">
         <f t="shared" si="6"/>
@@ -2446,11 +2446,11 @@
       </c>
       <c r="M28" s="19">
         <f t="shared" si="6"/>
-        <v>-498</v>
+        <v>-4404</v>
       </c>
       <c r="N28" s="19">
         <f t="shared" si="6"/>
-        <v>991.04000000000087</v>
+        <v>-3744.9599999999991</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -2459,55 +2459,55 @@
       </c>
       <c r="B29" s="19">
         <f>N29</f>
-        <v>-9255.82</v>
+        <v>-41029.82</v>
       </c>
       <c r="C29" s="19">
         <f t="shared" ref="C29:N29" si="7">C7+C28</f>
-        <v>4638</v>
+        <v>1638</v>
       </c>
       <c r="D29" s="19">
         <f t="shared" si="7"/>
-        <v>2828</v>
+        <v>-172</v>
       </c>
       <c r="E29" s="19">
         <f t="shared" si="7"/>
-        <v>163.93000000000029</v>
+        <v>-5602.0699999999988</v>
       </c>
       <c r="F29" s="19">
         <f t="shared" si="7"/>
-        <v>-3998.3600000000006</v>
+        <v>-11490.36</v>
       </c>
       <c r="G29" s="19">
         <f t="shared" si="7"/>
-        <v>-5471.6100000000006</v>
+        <v>-15519.61</v>
       </c>
       <c r="H29" s="19">
         <f t="shared" si="7"/>
-        <v>-5703.5400000000009</v>
+        <v>-19607.54</v>
       </c>
       <c r="I29" s="19">
         <f t="shared" si="7"/>
-        <v>-7433.68</v>
+        <v>-24153.68</v>
       </c>
       <c r="J29" s="19">
         <f t="shared" si="7"/>
-        <v>-7674.7900000000009</v>
+        <v>-28040.79</v>
       </c>
       <c r="K29" s="19">
         <f t="shared" si="7"/>
-        <v>-9138.86</v>
+        <v>-32270.86</v>
       </c>
       <c r="L29" s="19">
         <f t="shared" si="7"/>
-        <v>-9748.86</v>
+        <v>-32880.86</v>
       </c>
       <c r="M29" s="19">
         <f t="shared" si="7"/>
-        <v>-10246.86</v>
+        <v>-37284.86</v>
       </c>
       <c r="N29" s="19">
         <f t="shared" si="7"/>
-        <v>-9255.82</v>
+        <v>-41029.82</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -2622,11 +2622,11 @@
       </c>
       <c r="B34" s="19">
         <f>SUM(C34:N34)</f>
-        <v>16255.82</v>
+        <v>48029.82</v>
       </c>
       <c r="C34" s="19">
         <f t="shared" ref="C34:N34" si="9">C26-C9-C10-C14</f>
-        <v>2362</v>
+        <v>5362</v>
       </c>
       <c r="D34" s="19">
         <f t="shared" si="9"/>
@@ -2634,31 +2634,31 @@
       </c>
       <c r="E34" s="19">
         <f t="shared" si="9"/>
-        <v>2664.0699999999997</v>
+        <v>5430.0699999999988</v>
       </c>
       <c r="F34" s="19">
         <f t="shared" si="9"/>
-        <v>4162.2900000000009</v>
+        <v>5888.2900000000009</v>
       </c>
       <c r="G34" s="19">
         <f t="shared" si="9"/>
-        <v>1473.25</v>
+        <v>4029.25</v>
       </c>
       <c r="H34" s="19">
         <f t="shared" si="9"/>
-        <v>231.93000000000029</v>
+        <v>4087.9300000000003</v>
       </c>
       <c r="I34" s="19">
         <f t="shared" si="9"/>
-        <v>1730.1399999999994</v>
+        <v>4546.1399999999994</v>
       </c>
       <c r="J34" s="19">
         <f t="shared" si="9"/>
-        <v>241.11000000000058</v>
+        <v>3887.1100000000006</v>
       </c>
       <c r="K34" s="19">
         <f t="shared" si="9"/>
-        <v>1464.0699999999997</v>
+        <v>4230.0699999999988</v>
       </c>
       <c r="L34" s="19">
         <f t="shared" si="9"/>
@@ -2666,11 +2666,11 @@
       </c>
       <c r="M34" s="19">
         <f t="shared" si="9"/>
-        <v>498</v>
+        <v>4404</v>
       </c>
       <c r="N34" s="19">
         <f t="shared" si="9"/>
-        <v>-991.04000000000087</v>
+        <v>3744.9599999999991</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -2680,51 +2680,51 @@
       <c r="B35" s="2"/>
       <c r="C35" s="21">
         <f t="shared" ref="C35:N35" si="10">IF(C34&gt;0,IF(C30&lt;&gt;"",C30,C29)/C34,0)</f>
-        <v>1.9635901778154106</v>
+        <v>0.30548302872062666</v>
       </c>
       <c r="D35" s="21">
         <f t="shared" si="10"/>
-        <v>1.5624309392265194</v>
+        <v>-9.5027624309392267E-2</v>
       </c>
       <c r="E35" s="21">
         <f t="shared" si="10"/>
-        <v>6.1533668409613974E-2</v>
+        <v>-1.0316754664304513</v>
       </c>
       <c r="F35" s="21">
         <f t="shared" si="10"/>
-        <v>-0.96061543044814268</v>
+        <v>-1.9513916603971611</v>
       </c>
       <c r="G35" s="21">
         <f t="shared" si="10"/>
-        <v>-3.7139725097573395</v>
+        <v>-3.8517366755599678</v>
       </c>
       <c r="H35" s="21">
         <f t="shared" si="10"/>
-        <v>-24.591644030526425</v>
+        <v>-4.7964471015893126</v>
       </c>
       <c r="I35" s="21">
         <f t="shared" si="10"/>
-        <v>-4.296577155605906</v>
+        <v>-5.3130083983335323</v>
       </c>
       <c r="J35" s="21">
         <f t="shared" si="10"/>
-        <v>-31.831072954253173</v>
+        <v>-7.2137886501796959</v>
       </c>
       <c r="K35" s="21">
         <f t="shared" si="10"/>
-        <v>-6.2420922496875164</v>
+        <v>-7.6289186703766152</v>
       </c>
       <c r="L35" s="21">
         <f t="shared" si="10"/>
-        <v>-15.981737704918034</v>
+        <v>-53.903049180327869</v>
       </c>
       <c r="M35" s="21">
         <f t="shared" si="10"/>
-        <v>-20.576024096385542</v>
+        <v>-8.4661353315168029</v>
       </c>
       <c r="N35" s="21">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>-10.956010211056997</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -2797,20 +2797,20 @@
       <c r="A7" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="B7" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="C7" s="32"/>
+      <c r="B7" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="33"/>
     </row>
     <row r="8" spans="1:3" ht="25" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
         <v>87</v>
       </c>
       <c r="B8" s="27">
-        <v>1568</v>
+        <v>4002</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="25" x14ac:dyDescent="0.25">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="B9" s="26">
         <f>IFERROR(AVERAGEIF('Suivi mensuel'!C34:N34,"&gt;0"),0)</f>
-        <v>1567.8963636363637</v>
+        <v>4002.4850000000001</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>89</v>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B10" s="29">
         <f>IF(B8&gt;0,B6/B8,0)</f>
-        <v>4.4642857142857144</v>
+        <v>1.7491254372813594</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>90</v>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="B11" s="30">
         <f>IF(AND(B10&gt;0,B5&gt;0),EDATE(B5,INT(B10)),"")</f>
-        <v>46447</v>
+        <v>46357</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>92</v>

--- a/2 FINANCE/TRESORERIE/2026 1027 Modèle - Trésorerie et mois de survie.xlsx
+++ b/2 FINANCE/TRESORERIE/2026 1027 Modèle - Trésorerie et mois de survie.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vians\Documents\Claude\Projects\HEC-GEMM-Groupe-7\2 FINANCE\TRESORERIE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DE7D47A-DECD-4C97-8966-7DA43DBA166E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27CF0783-8306-4946-9708-553BFE749122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{2D54D8BB-BD50-4D46-AD8E-735E0D6561AC}"/>
   </bookViews>
@@ -350,7 +350,7 @@
     <t>H : moyenne des mois à consommation positive de la simulation (ligne 9), à remplacer par la consommation constatée</t>
   </si>
   <si>
-    <t>SIMULATION mise à jour le 28/10/2026 : flux repris du budget prévisionnel (H), y compris le staffing des Opérations et les investissements de l'année 1 (en novembre, dans « Autres décaissements »), sans TVA ni délais de paiement. À remplacer par les montants constatés.</t>
+    <t>SIMULATION mise à jour le 28/10/2026 : flux repris du budget prévisionnel (H), y compris le staffing des Opérations (scénario S3, et équipe complète pour les deux pilotes, dans « Matières, boissons et extras ») et les investissements de l'année 1 (en novembre, dans « Autres décaissements »), sans TVA ni délais de paiement. À remplacer par les montants constatés.</t>
   </si>
 </sst>
 </file>
@@ -1526,31 +1526,31 @@
       </c>
       <c r="H7" s="18">
         <f t="shared" si="1"/>
-        <v>-15519.61</v>
+        <v>-14819.61</v>
       </c>
       <c r="I7" s="18">
         <f t="shared" si="1"/>
-        <v>-19607.54</v>
+        <v>-18207.54</v>
       </c>
       <c r="J7" s="18">
         <f t="shared" si="1"/>
-        <v>-24153.68</v>
+        <v>-22298.68</v>
       </c>
       <c r="K7" s="18">
         <f t="shared" si="1"/>
-        <v>-28040.79</v>
+        <v>-25485.79</v>
       </c>
       <c r="L7" s="18">
         <f t="shared" si="1"/>
-        <v>-32270.86</v>
+        <v>-29015.86</v>
       </c>
       <c r="M7" s="18">
         <f t="shared" si="1"/>
-        <v>-32880.86</v>
+        <v>-29625.86</v>
       </c>
       <c r="N7" s="18">
         <f t="shared" si="1"/>
-        <v>-37284.86</v>
+        <v>-33574.86</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="B19" s="18">
         <f t="shared" si="4"/>
-        <v>70121</v>
+        <v>65711</v>
       </c>
       <c r="C19" s="17">
         <v>0</v>
@@ -2027,28 +2027,28 @@
         <v>5732</v>
       </c>
       <c r="G19" s="17">
-        <v>5764</v>
+        <v>5064</v>
       </c>
       <c r="H19" s="17">
-        <v>8091</v>
+        <v>7391</v>
       </c>
       <c r="I19" s="17">
-        <v>8572</v>
+        <v>8117</v>
       </c>
       <c r="J19" s="17">
-        <v>8604</v>
+        <v>7904</v>
       </c>
       <c r="K19" s="17">
-        <v>5251</v>
+        <v>4551</v>
       </c>
       <c r="L19" s="17">
         <v>0</v>
       </c>
       <c r="M19" s="17">
-        <v>11412</v>
+        <v>10957</v>
       </c>
       <c r="N19" s="17">
-        <v>11444</v>
+        <v>10744</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="B26" s="19">
         <f t="shared" si="4"/>
-        <v>169985.16999999998</v>
+        <v>165575.16999999998</v>
       </c>
       <c r="C26" s="19">
         <f t="shared" ref="C26:N26" si="5">SUM(C17:C25)</f>
@@ -2347,23 +2347,23 @@
       </c>
       <c r="G26" s="19">
         <f t="shared" si="5"/>
-        <v>11154.25</v>
+        <v>10454.25</v>
       </c>
       <c r="H26" s="19">
         <f t="shared" si="5"/>
-        <v>17043.29</v>
+        <v>16343.29</v>
       </c>
       <c r="I26" s="19">
         <f t="shared" si="5"/>
-        <v>22439</v>
+        <v>21984</v>
       </c>
       <c r="J26" s="19">
         <f t="shared" si="5"/>
-        <v>19047.82</v>
+        <v>18347.82</v>
       </c>
       <c r="K26" s="19">
         <f t="shared" si="5"/>
-        <v>9149.7099999999991</v>
+        <v>8449.7099999999991</v>
       </c>
       <c r="L26" s="19">
         <f t="shared" si="5"/>
@@ -2371,11 +2371,11 @@
       </c>
       <c r="M26" s="19">
         <f t="shared" si="5"/>
-        <v>30332.57</v>
+        <v>29877.57</v>
       </c>
       <c r="N26" s="19">
         <f t="shared" si="5"/>
-        <v>26941.39</v>
+        <v>26241.39</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="B28" s="19">
         <f>SUM(C28:N28)</f>
-        <v>-41029.82</v>
+        <v>-36619.82</v>
       </c>
       <c r="C28" s="19">
         <f t="shared" ref="C28:N28" si="6">C15-C26</f>
@@ -2422,23 +2422,23 @@
       </c>
       <c r="G28" s="19">
         <f t="shared" si="6"/>
-        <v>-4029.25</v>
+        <v>-3329.25</v>
       </c>
       <c r="H28" s="19">
         <f t="shared" si="6"/>
-        <v>-4087.9300000000003</v>
+        <v>-3387.9300000000003</v>
       </c>
       <c r="I28" s="19">
         <f t="shared" si="6"/>
-        <v>-4546.1399999999994</v>
+        <v>-4091.1399999999994</v>
       </c>
       <c r="J28" s="19">
         <f t="shared" si="6"/>
-        <v>-3887.1100000000006</v>
+        <v>-3187.1100000000006</v>
       </c>
       <c r="K28" s="19">
         <f t="shared" si="6"/>
-        <v>-4230.0699999999988</v>
+        <v>-3530.0699999999988</v>
       </c>
       <c r="L28" s="19">
         <f t="shared" si="6"/>
@@ -2446,11 +2446,11 @@
       </c>
       <c r="M28" s="19">
         <f t="shared" si="6"/>
-        <v>-4404</v>
+        <v>-3949</v>
       </c>
       <c r="N28" s="19">
         <f t="shared" si="6"/>
-        <v>-3744.9599999999991</v>
+        <v>-3044.9599999999991</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="B29" s="19">
         <f>N29</f>
-        <v>-41029.82</v>
+        <v>-36619.82</v>
       </c>
       <c r="C29" s="19">
         <f t="shared" ref="C29:N29" si="7">C7+C28</f>
@@ -2479,35 +2479,35 @@
       </c>
       <c r="G29" s="19">
         <f t="shared" si="7"/>
-        <v>-15519.61</v>
+        <v>-14819.61</v>
       </c>
       <c r="H29" s="19">
         <f t="shared" si="7"/>
-        <v>-19607.54</v>
+        <v>-18207.54</v>
       </c>
       <c r="I29" s="19">
         <f t="shared" si="7"/>
-        <v>-24153.68</v>
+        <v>-22298.68</v>
       </c>
       <c r="J29" s="19">
         <f t="shared" si="7"/>
-        <v>-28040.79</v>
+        <v>-25485.79</v>
       </c>
       <c r="K29" s="19">
         <f t="shared" si="7"/>
-        <v>-32270.86</v>
+        <v>-29015.86</v>
       </c>
       <c r="L29" s="19">
         <f t="shared" si="7"/>
-        <v>-32880.86</v>
+        <v>-29625.86</v>
       </c>
       <c r="M29" s="19">
         <f t="shared" si="7"/>
-        <v>-37284.86</v>
+        <v>-33574.86</v>
       </c>
       <c r="N29" s="19">
         <f t="shared" si="7"/>
-        <v>-41029.82</v>
+        <v>-36619.82</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="B34" s="19">
         <f>SUM(C34:N34)</f>
-        <v>48029.82</v>
+        <v>43619.82</v>
       </c>
       <c r="C34" s="19">
         <f t="shared" ref="C34:N34" si="9">C26-C9-C10-C14</f>
@@ -2642,23 +2642,23 @@
       </c>
       <c r="G34" s="19">
         <f t="shared" si="9"/>
-        <v>4029.25</v>
+        <v>3329.25</v>
       </c>
       <c r="H34" s="19">
         <f t="shared" si="9"/>
-        <v>4087.9300000000003</v>
+        <v>3387.9300000000003</v>
       </c>
       <c r="I34" s="19">
         <f t="shared" si="9"/>
-        <v>4546.1399999999994</v>
+        <v>4091.1399999999994</v>
       </c>
       <c r="J34" s="19">
         <f t="shared" si="9"/>
-        <v>3887.1100000000006</v>
+        <v>3187.1100000000006</v>
       </c>
       <c r="K34" s="19">
         <f t="shared" si="9"/>
-        <v>4230.0699999999988</v>
+        <v>3530.0699999999988</v>
       </c>
       <c r="L34" s="19">
         <f t="shared" si="9"/>
@@ -2666,11 +2666,11 @@
       </c>
       <c r="M34" s="19">
         <f t="shared" si="9"/>
-        <v>4404</v>
+        <v>3949</v>
       </c>
       <c r="N34" s="19">
         <f t="shared" si="9"/>
-        <v>3744.9599999999991</v>
+        <v>3044.9599999999991</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -2696,35 +2696,35 @@
       </c>
       <c r="G35" s="21">
         <f t="shared" si="10"/>
-        <v>-3.8517366755599678</v>
+        <v>-4.4513358864609147</v>
       </c>
       <c r="H35" s="21">
         <f t="shared" si="10"/>
-        <v>-4.7964471015893126</v>
+        <v>-5.3742373661793481</v>
       </c>
       <c r="I35" s="21">
         <f t="shared" si="10"/>
-        <v>-5.3130083983335323</v>
+        <v>-5.4504807950840117</v>
       </c>
       <c r="J35" s="21">
         <f t="shared" si="10"/>
-        <v>-7.2137886501796959</v>
+        <v>-7.9965203585693612</v>
       </c>
       <c r="K35" s="21">
         <f t="shared" si="10"/>
-        <v>-7.6289186703766152</v>
+        <v>-8.2196273728283042</v>
       </c>
       <c r="L35" s="21">
         <f t="shared" si="10"/>
-        <v>-53.903049180327869</v>
+        <v>-48.566983606557379</v>
       </c>
       <c r="M35" s="21">
         <f t="shared" si="10"/>
-        <v>-8.4661353315168029</v>
+        <v>-8.5021169916434545</v>
       </c>
       <c r="N35" s="21">
         <f t="shared" si="10"/>
-        <v>-10.956010211056997</v>
+        <v>-12.026371446587151</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -2807,7 +2807,7 @@
         <v>87</v>
       </c>
       <c r="B8" s="27">
-        <v>4002</v>
+        <v>3635</v>
       </c>
       <c r="C8" s="28" t="s">
         <v>101</v>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="B9" s="26">
         <f>IFERROR(AVERAGEIF('Suivi mensuel'!C34:N34,"&gt;0"),0)</f>
-        <v>4002.4850000000001</v>
+        <v>3634.9850000000001</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>89</v>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B10" s="29">
         <f>IF(B8&gt;0,B6/B8,0)</f>
-        <v>1.7491254372813594</v>
+        <v>1.9257221458046767</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>90</v>

--- a/2 FINANCE/TRESORERIE/2026 1027 Modèle - Trésorerie et mois de survie.xlsx
+++ b/2 FINANCE/TRESORERIE/2026 1027 Modèle - Trésorerie et mois de survie.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vians\Documents\Claude\Projects\HEC-GEMM-Groupe-7\2 FINANCE\TRESORERIE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27CF0783-8306-4946-9708-553BFE749122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2504E7E5-0BC1-4580-9D16-6916FE5C5733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{2D54D8BB-BD50-4D46-AD8E-735E0D6561AC}"/>
   </bookViews>
@@ -350,7 +350,7 @@
     <t>H : moyenne des mois à consommation positive de la simulation (ligne 9), à remplacer par la consommation constatée</t>
   </si>
   <si>
-    <t>SIMULATION mise à jour le 28/10/2026 : flux repris du budget prévisionnel (H), y compris le staffing des Opérations (scénario S3, et équipe complète pour les deux pilotes, dans « Matières, boissons et extras ») et les investissements de l'année 1 (en novembre, dans « Autres décaissements »), sans TVA ni délais de paiement. À remplacer par les montants constatés.</t>
+    <t>SIMULATION mise à jour le 28/10/2026 : flux repris du budget prévisionnel (H), y compris le staffing des Opérations (scénario S3, et équipe complète pour les deux pilotes, dans « Matières, boissons et extras ») et les investissements de l'année 1 (en novembre, dans « Autres décaissements »), avec la TVA (onglet TVA du modèle Prévisions : ventes encaissées TTC ; TVA payée aux fournisseurs et reversée à l'État dans « Impôts et TVA » ; crédit de TVA reporté, sans demande de remboursement), sans délais de paiement. À remplacer par les montants constatés.</t>
   </si>
 </sst>
 </file>
@@ -1510,47 +1510,47 @@
       </c>
       <c r="D7" s="18">
         <f t="shared" ref="D7:N7" si="1">IF(C30&lt;&gt;"",C30,C29)</f>
-        <v>1638</v>
+        <v>637</v>
       </c>
       <c r="E7" s="18">
         <f t="shared" si="1"/>
-        <v>-172</v>
+        <v>-1514</v>
       </c>
       <c r="F7" s="18">
         <f t="shared" si="1"/>
-        <v>-5602.0699999999988</v>
+        <v>-8015.3899999999994</v>
       </c>
       <c r="G7" s="18">
         <f t="shared" si="1"/>
-        <v>-11490.36</v>
+        <v>-14815.36</v>
       </c>
       <c r="H7" s="18">
         <f t="shared" si="1"/>
-        <v>-14819.61</v>
+        <v>-18713.810000000001</v>
       </c>
       <c r="I7" s="18">
         <f t="shared" si="1"/>
-        <v>-18207.54</v>
+        <v>-22944.99</v>
       </c>
       <c r="J7" s="18">
         <f t="shared" si="1"/>
-        <v>-22298.68</v>
+        <v>-27768.750000000004</v>
       </c>
       <c r="K7" s="18">
         <f t="shared" si="1"/>
-        <v>-25485.79</v>
+        <v>-31676.980000000003</v>
       </c>
       <c r="L7" s="18">
         <f t="shared" si="1"/>
-        <v>-29015.86</v>
+        <v>-35898.370000000003</v>
       </c>
       <c r="M7" s="18">
         <f t="shared" si="1"/>
-        <v>-29625.86</v>
+        <v>-36609.370000000003</v>
       </c>
       <c r="N7" s="18">
         <f t="shared" si="1"/>
-        <v>-33574.86</v>
+        <v>-41442.910000000003</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="B9" s="18">
         <f t="shared" ref="B9:B15" si="2">SUM(C9:N9)</f>
-        <v>121955.34999999998</v>
+        <v>136590</v>
       </c>
       <c r="C9" s="17">
         <v>0</v>
@@ -1586,34 +1586,34 @@
         <v>0</v>
       </c>
       <c r="E9" s="17">
-        <v>4919.6400000000003</v>
+        <v>5510</v>
       </c>
       <c r="F9" s="17">
-        <v>9857.14</v>
+        <v>11040</v>
       </c>
       <c r="G9" s="17">
-        <v>7125</v>
+        <v>7980</v>
       </c>
       <c r="H9" s="17">
-        <v>12955.36</v>
+        <v>14510</v>
       </c>
       <c r="I9" s="17">
-        <v>17892.86</v>
+        <v>20040</v>
       </c>
       <c r="J9" s="17">
-        <v>15160.71</v>
+        <v>16980</v>
       </c>
       <c r="K9" s="17">
-        <v>4919.6400000000003</v>
+        <v>5510</v>
       </c>
       <c r="L9" s="17">
         <v>0</v>
       </c>
       <c r="M9" s="17">
-        <v>25928.57</v>
+        <v>29040</v>
       </c>
       <c r="N9" s="17">
-        <v>23196.43</v>
+        <v>25980</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B15" s="19">
         <f t="shared" si="2"/>
-        <v>128955.34999999998</v>
+        <v>143590</v>
       </c>
       <c r="C15" s="19">
         <f t="shared" ref="C15:N15" si="3">SUM(C9:C14)</f>
@@ -1859,31 +1859,31 @@
       </c>
       <c r="E15" s="19">
         <f t="shared" si="3"/>
-        <v>4919.6400000000003</v>
+        <v>5510</v>
       </c>
       <c r="F15" s="19">
         <f t="shared" si="3"/>
-        <v>9857.14</v>
+        <v>11040</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="3"/>
-        <v>7125</v>
+        <v>7980</v>
       </c>
       <c r="H15" s="19">
         <f t="shared" si="3"/>
-        <v>12955.36</v>
+        <v>14510</v>
       </c>
       <c r="I15" s="19">
         <f t="shared" si="3"/>
-        <v>17892.86</v>
+        <v>20040</v>
       </c>
       <c r="J15" s="19">
         <f t="shared" si="3"/>
-        <v>15160.71</v>
+        <v>16980</v>
       </c>
       <c r="K15" s="19">
         <f t="shared" si="3"/>
-        <v>4919.6400000000003</v>
+        <v>5510</v>
       </c>
       <c r="L15" s="19">
         <f t="shared" si="3"/>
@@ -1891,11 +1891,11 @@
       </c>
       <c r="M15" s="19">
         <f t="shared" si="3"/>
-        <v>25928.57</v>
+        <v>29040</v>
       </c>
       <c r="N15" s="19">
         <f t="shared" si="3"/>
-        <v>23196.43</v>
+        <v>25980</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -2237,43 +2237,43 @@
       </c>
       <c r="B24" s="18">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>23375.760000000002</v>
       </c>
       <c r="C24" s="17">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="D24" s="17">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="E24" s="17">
-        <v>0</v>
+        <v>1661.68</v>
       </c>
       <c r="F24" s="17">
-        <v>0</v>
+        <v>2094.54</v>
       </c>
       <c r="G24" s="17">
-        <v>0</v>
+        <v>1424.2</v>
       </c>
       <c r="H24" s="17">
-        <v>0</v>
+        <v>2397.89</v>
       </c>
       <c r="I24" s="17">
-        <v>0</v>
+        <v>2879.76</v>
       </c>
       <c r="J24" s="17">
-        <v>0</v>
+        <v>2540.41</v>
       </c>
       <c r="K24" s="17">
-        <v>0</v>
+        <v>1281.68</v>
       </c>
       <c r="L24" s="17">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M24" s="17">
-        <v>0</v>
+        <v>3995.97</v>
       </c>
       <c r="N24" s="17">
-        <v>0</v>
+        <v>3656.63</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -2327,55 +2327,55 @@
       </c>
       <c r="B26" s="19">
         <f t="shared" si="4"/>
-        <v>165575.16999999998</v>
+        <v>188950.93</v>
       </c>
       <c r="C26" s="19">
         <f t="shared" ref="C26:N26" si="5">SUM(C17:C25)</f>
-        <v>5362</v>
+        <v>6363</v>
       </c>
       <c r="D26" s="19">
         <f t="shared" si="5"/>
-        <v>1810</v>
+        <v>2151</v>
       </c>
       <c r="E26" s="19">
         <f t="shared" si="5"/>
-        <v>10349.709999999999</v>
+        <v>12011.39</v>
       </c>
       <c r="F26" s="19">
         <f t="shared" si="5"/>
-        <v>15745.43</v>
+        <v>17839.97</v>
       </c>
       <c r="G26" s="19">
         <f t="shared" si="5"/>
-        <v>10454.25</v>
+        <v>11878.45</v>
       </c>
       <c r="H26" s="19">
         <f t="shared" si="5"/>
-        <v>16343.29</v>
+        <v>18741.18</v>
       </c>
       <c r="I26" s="19">
         <f t="shared" si="5"/>
-        <v>21984</v>
+        <v>24863.760000000002</v>
       </c>
       <c r="J26" s="19">
         <f t="shared" si="5"/>
-        <v>18347.82</v>
+        <v>20888.23</v>
       </c>
       <c r="K26" s="19">
         <f t="shared" si="5"/>
-        <v>8449.7099999999991</v>
+        <v>9731.39</v>
       </c>
       <c r="L26" s="19">
         <f t="shared" si="5"/>
-        <v>610</v>
+        <v>711</v>
       </c>
       <c r="M26" s="19">
         <f t="shared" si="5"/>
-        <v>29877.57</v>
+        <v>33873.54</v>
       </c>
       <c r="N26" s="19">
         <f t="shared" si="5"/>
-        <v>26241.39</v>
+        <v>29898.02</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -2402,55 +2402,55 @@
       </c>
       <c r="B28" s="19">
         <f>SUM(C28:N28)</f>
-        <v>-36619.82</v>
+        <v>-45360.930000000008</v>
       </c>
       <c r="C28" s="19">
         <f t="shared" ref="C28:N28" si="6">C15-C26</f>
-        <v>1638</v>
+        <v>637</v>
       </c>
       <c r="D28" s="19">
         <f t="shared" si="6"/>
-        <v>-1810</v>
+        <v>-2151</v>
       </c>
       <c r="E28" s="19">
         <f t="shared" si="6"/>
-        <v>-5430.0699999999988</v>
+        <v>-6501.3899999999994</v>
       </c>
       <c r="F28" s="19">
         <f t="shared" si="6"/>
-        <v>-5888.2900000000009</v>
+        <v>-6799.9700000000012</v>
       </c>
       <c r="G28" s="19">
         <f t="shared" si="6"/>
-        <v>-3329.25</v>
+        <v>-3898.4500000000007</v>
       </c>
       <c r="H28" s="19">
         <f t="shared" si="6"/>
-        <v>-3387.9300000000003</v>
+        <v>-4231.18</v>
       </c>
       <c r="I28" s="19">
         <f t="shared" si="6"/>
-        <v>-4091.1399999999994</v>
+        <v>-4823.760000000002</v>
       </c>
       <c r="J28" s="19">
         <f t="shared" si="6"/>
-        <v>-3187.1100000000006</v>
+        <v>-3908.2299999999996</v>
       </c>
       <c r="K28" s="19">
         <f t="shared" si="6"/>
-        <v>-3530.0699999999988</v>
+        <v>-4221.3899999999994</v>
       </c>
       <c r="L28" s="19">
         <f t="shared" si="6"/>
-        <v>-610</v>
+        <v>-711</v>
       </c>
       <c r="M28" s="19">
         <f t="shared" si="6"/>
-        <v>-3949</v>
+        <v>-4833.5400000000009</v>
       </c>
       <c r="N28" s="19">
         <f t="shared" si="6"/>
-        <v>-3044.9599999999991</v>
+        <v>-3918.0200000000004</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -2459,55 +2459,55 @@
       </c>
       <c r="B29" s="19">
         <f>N29</f>
-        <v>-36619.82</v>
+        <v>-45360.930000000008</v>
       </c>
       <c r="C29" s="19">
         <f t="shared" ref="C29:N29" si="7">C7+C28</f>
-        <v>1638</v>
+        <v>637</v>
       </c>
       <c r="D29" s="19">
         <f t="shared" si="7"/>
-        <v>-172</v>
+        <v>-1514</v>
       </c>
       <c r="E29" s="19">
         <f t="shared" si="7"/>
-        <v>-5602.0699999999988</v>
+        <v>-8015.3899999999994</v>
       </c>
       <c r="F29" s="19">
         <f t="shared" si="7"/>
-        <v>-11490.36</v>
+        <v>-14815.36</v>
       </c>
       <c r="G29" s="19">
         <f t="shared" si="7"/>
-        <v>-14819.61</v>
+        <v>-18713.810000000001</v>
       </c>
       <c r="H29" s="19">
         <f t="shared" si="7"/>
-        <v>-18207.54</v>
+        <v>-22944.99</v>
       </c>
       <c r="I29" s="19">
         <f t="shared" si="7"/>
-        <v>-22298.68</v>
+        <v>-27768.750000000004</v>
       </c>
       <c r="J29" s="19">
         <f t="shared" si="7"/>
-        <v>-25485.79</v>
+        <v>-31676.980000000003</v>
       </c>
       <c r="K29" s="19">
         <f t="shared" si="7"/>
-        <v>-29015.86</v>
+        <v>-35898.370000000003</v>
       </c>
       <c r="L29" s="19">
         <f t="shared" si="7"/>
-        <v>-29625.86</v>
+        <v>-36609.370000000003</v>
       </c>
       <c r="M29" s="19">
         <f t="shared" si="7"/>
-        <v>-33574.86</v>
+        <v>-41442.910000000003</v>
       </c>
       <c r="N29" s="19">
         <f t="shared" si="7"/>
-        <v>-36619.82</v>
+        <v>-45360.930000000008</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -2622,55 +2622,55 @@
       </c>
       <c r="B34" s="19">
         <f>SUM(C34:N34)</f>
-        <v>43619.82</v>
+        <v>52360.929999999993</v>
       </c>
       <c r="C34" s="19">
         <f t="shared" ref="C34:N34" si="9">C26-C9-C10-C14</f>
-        <v>5362</v>
+        <v>6363</v>
       </c>
       <c r="D34" s="19">
         <f t="shared" si="9"/>
-        <v>1810</v>
+        <v>2151</v>
       </c>
       <c r="E34" s="19">
         <f t="shared" si="9"/>
-        <v>5430.0699999999988</v>
+        <v>6501.3899999999994</v>
       </c>
       <c r="F34" s="19">
         <f t="shared" si="9"/>
-        <v>5888.2900000000009</v>
+        <v>6799.9700000000012</v>
       </c>
       <c r="G34" s="19">
         <f t="shared" si="9"/>
-        <v>3329.25</v>
+        <v>3898.4500000000007</v>
       </c>
       <c r="H34" s="19">
         <f t="shared" si="9"/>
-        <v>3387.9300000000003</v>
+        <v>4231.18</v>
       </c>
       <c r="I34" s="19">
         <f t="shared" si="9"/>
-        <v>4091.1399999999994</v>
+        <v>4823.760000000002</v>
       </c>
       <c r="J34" s="19">
         <f t="shared" si="9"/>
-        <v>3187.1100000000006</v>
+        <v>3908.2299999999996</v>
       </c>
       <c r="K34" s="19">
         <f t="shared" si="9"/>
-        <v>3530.0699999999988</v>
+        <v>4221.3899999999994</v>
       </c>
       <c r="L34" s="19">
         <f t="shared" si="9"/>
-        <v>610</v>
+        <v>711</v>
       </c>
       <c r="M34" s="19">
         <f t="shared" si="9"/>
-        <v>3949</v>
+        <v>4833.5400000000009</v>
       </c>
       <c r="N34" s="19">
         <f t="shared" si="9"/>
-        <v>3044.9599999999991</v>
+        <v>3918.0200000000004</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -2680,51 +2680,51 @@
       <c r="B35" s="2"/>
       <c r="C35" s="21">
         <f t="shared" ref="C35:N35" si="10">IF(C34&gt;0,IF(C30&lt;&gt;"",C30,C29)/C34,0)</f>
-        <v>0.30548302872062666</v>
+        <v>0.1001100110011001</v>
       </c>
       <c r="D35" s="21">
         <f t="shared" si="10"/>
-        <v>-9.5027624309392267E-2</v>
+        <v>-0.70385867038586702</v>
       </c>
       <c r="E35" s="21">
         <f t="shared" si="10"/>
-        <v>-1.0316754664304513</v>
+        <v>-1.2328732778682712</v>
       </c>
       <c r="F35" s="21">
         <f t="shared" si="10"/>
-        <v>-1.9513916603971611</v>
+        <v>-2.1787390238486344</v>
       </c>
       <c r="G35" s="21">
         <f t="shared" si="10"/>
-        <v>-4.4513358864609147</v>
+        <v>-4.8003206402544594</v>
       </c>
       <c r="H35" s="21">
         <f t="shared" si="10"/>
-        <v>-5.3742373661793481</v>
+        <v>-5.4228347647701112</v>
       </c>
       <c r="I35" s="21">
         <f t="shared" si="10"/>
-        <v>-5.4504807950840117</v>
+        <v>-5.7566607791432389</v>
       </c>
       <c r="J35" s="21">
         <f t="shared" si="10"/>
-        <v>-7.9965203585693612</v>
+        <v>-8.105198516975717</v>
       </c>
       <c r="K35" s="21">
         <f t="shared" si="10"/>
-        <v>-8.2196273728283042</v>
+        <v>-8.5039216940391693</v>
       </c>
       <c r="L35" s="21">
         <f t="shared" si="10"/>
-        <v>-48.566983606557379</v>
+        <v>-51.489971870604784</v>
       </c>
       <c r="M35" s="21">
         <f t="shared" si="10"/>
-        <v>-8.5021169916434545</v>
+        <v>-8.5740285587788652</v>
       </c>
       <c r="N35" s="21">
         <f t="shared" si="10"/>
-        <v>-12.026371446587151</v>
+        <v>-11.577513642094733</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -2807,7 +2807,7 @@
         <v>87</v>
       </c>
       <c r="B8" s="27">
-        <v>3635</v>
+        <v>4363</v>
       </c>
       <c r="C8" s="28" t="s">
         <v>101</v>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="B9" s="26">
         <f>IFERROR(AVERAGEIF('Suivi mensuel'!C34:N34,"&gt;0"),0)</f>
-        <v>3634.9850000000001</v>
+        <v>4363.4108333333324</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>89</v>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B10" s="29">
         <f>IF(B8&gt;0,B6/B8,0)</f>
-        <v>1.9257221458046767</v>
+        <v>1.6044006417602568</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>90</v>

--- a/2 FINANCE/TRESORERIE/2026 1027 Modèle - Trésorerie et mois de survie.xlsx
+++ b/2 FINANCE/TRESORERIE/2026 1027 Modèle - Trésorerie et mois de survie.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vians\Documents\Claude\Projects\HEC-GEMM-Groupe-7\2 FINANCE\TRESORERIE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2504E7E5-0BC1-4580-9D16-6916FE5C5733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0BA43A9-B9B0-46B0-965B-AAFF6C535A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{2D54D8BB-BD50-4D46-AD8E-735E0D6561AC}"/>
   </bookViews>
@@ -350,7 +350,7 @@
     <t>H : moyenne des mois à consommation positive de la simulation (ligne 9), à remplacer par la consommation constatée</t>
   </si>
   <si>
-    <t>SIMULATION mise à jour le 28/10/2026 : flux repris du budget prévisionnel (H), y compris le staffing des Opérations (scénario S3, et équipe complète pour les deux pilotes, dans « Matières, boissons et extras ») et les investissements de l'année 1 (en novembre, dans « Autres décaissements »), avec la TVA (onglet TVA du modèle Prévisions : ventes encaissées TTC ; TVA payée aux fournisseurs et reversée à l'État dans « Impôts et TVA » ; crédit de TVA reporté, sans demande de remboursement), sans délais de paiement. À remplacer par les montants constatés.</t>
+    <t>SIMULATION mise à jour le 28/10/2026 : flux repris du budget prévisionnel (H), avec les hypothèses modifiées le 28/10/2026 par le responsable Finance (jauges 40 / 35 / 30 / 20, salle pleine, équipe à 15 ou 20 % du chiffre d'affaires, sans photographe ; surcoût d'équipe des pilotes dans « Matières, boissons et extras ») et les investissements de l'année 1 (en novembre, dans « Autres décaissements »), avec la TVA (onglet TVA du modèle Prévisions : ventes encaissées TTC ; TVA payée aux fournisseurs et reversée à l'État dans « Impôts et TVA » ; crédit de TVA reporté, sans demande de remboursement), sans délais de paiement. À remplacer par les montants constatés.</t>
   </si>
 </sst>
 </file>
@@ -1518,39 +1518,39 @@
       </c>
       <c r="F7" s="18">
         <f t="shared" si="1"/>
-        <v>-8015.3899999999994</v>
+        <v>-2015.989999999998</v>
       </c>
       <c r="G7" s="18">
         <f t="shared" si="1"/>
-        <v>-14815.36</v>
+        <v>-3893.2799999999988</v>
       </c>
       <c r="H7" s="18">
         <f t="shared" si="1"/>
-        <v>-18713.810000000001</v>
+        <v>-2830.5299999999988</v>
       </c>
       <c r="I7" s="18">
         <f t="shared" si="1"/>
-        <v>-22944.99</v>
+        <v>1248.1900000000023</v>
       </c>
       <c r="J7" s="18">
         <f t="shared" si="1"/>
-        <v>-27768.750000000004</v>
+        <v>3657.6200000000026</v>
       </c>
       <c r="K7" s="18">
         <f t="shared" si="1"/>
-        <v>-31676.980000000003</v>
+        <v>7021.0900000000038</v>
       </c>
       <c r="L7" s="18">
         <f t="shared" si="1"/>
-        <v>-35898.370000000003</v>
+        <v>8799.1000000000058</v>
       </c>
       <c r="M7" s="18">
         <f t="shared" si="1"/>
-        <v>-36609.370000000003</v>
+        <v>8088.1000000000058</v>
       </c>
       <c r="N7" s="18">
         <f t="shared" si="1"/>
-        <v>-41442.910000000003</v>
+        <v>12798.240000000005</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="B9" s="18">
         <f t="shared" ref="B9:B15" si="2">SUM(C9:N9)</f>
-        <v>136590</v>
+        <v>225000</v>
       </c>
       <c r="C9" s="17">
         <v>0</v>
@@ -1586,34 +1586,34 @@
         <v>0</v>
       </c>
       <c r="E9" s="17">
-        <v>5510</v>
+        <v>11600</v>
       </c>
       <c r="F9" s="17">
-        <v>11040</v>
+        <v>20700</v>
       </c>
       <c r="G9" s="17">
-        <v>7980</v>
+        <v>14700</v>
       </c>
       <c r="H9" s="17">
-        <v>14510</v>
+        <v>23600</v>
       </c>
       <c r="I9" s="17">
-        <v>20040</v>
+        <v>32700</v>
       </c>
       <c r="J9" s="17">
-        <v>16980</v>
+        <v>26700</v>
       </c>
       <c r="K9" s="17">
-        <v>5510</v>
+        <v>11600</v>
       </c>
       <c r="L9" s="17">
         <v>0</v>
       </c>
       <c r="M9" s="17">
-        <v>29040</v>
+        <v>44700</v>
       </c>
       <c r="N9" s="17">
-        <v>25980</v>
+        <v>38700</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B15" s="19">
         <f t="shared" si="2"/>
-        <v>143590</v>
+        <v>232000</v>
       </c>
       <c r="C15" s="19">
         <f t="shared" ref="C15:N15" si="3">SUM(C9:C14)</f>
@@ -1859,31 +1859,31 @@
       </c>
       <c r="E15" s="19">
         <f t="shared" si="3"/>
-        <v>5510</v>
+        <v>11600</v>
       </c>
       <c r="F15" s="19">
         <f t="shared" si="3"/>
-        <v>11040</v>
+        <v>20700</v>
       </c>
       <c r="G15" s="19">
         <f t="shared" si="3"/>
-        <v>7980</v>
+        <v>14700</v>
       </c>
       <c r="H15" s="19">
         <f t="shared" si="3"/>
-        <v>14510</v>
+        <v>23600</v>
       </c>
       <c r="I15" s="19">
         <f t="shared" si="3"/>
-        <v>20040</v>
+        <v>32700</v>
       </c>
       <c r="J15" s="19">
         <f t="shared" si="3"/>
-        <v>16980</v>
+        <v>26700</v>
       </c>
       <c r="K15" s="19">
         <f t="shared" si="3"/>
-        <v>5510</v>
+        <v>11600</v>
       </c>
       <c r="L15" s="19">
         <f t="shared" si="3"/>
@@ -1891,11 +1891,11 @@
       </c>
       <c r="M15" s="19">
         <f t="shared" si="3"/>
-        <v>29040</v>
+        <v>44700</v>
       </c>
       <c r="N15" s="19">
         <f t="shared" si="3"/>
-        <v>25980</v>
+        <v>38700</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="B19" s="18">
         <f t="shared" si="4"/>
-        <v>65711</v>
+        <v>84129.989999999991</v>
       </c>
       <c r="C19" s="17">
         <v>0</v>
@@ -2021,34 +2021,34 @@
         <v>0</v>
       </c>
       <c r="E19" s="17">
-        <v>5251</v>
+        <v>5653.57</v>
       </c>
       <c r="F19" s="17">
-        <v>5732</v>
+        <v>9131.43</v>
       </c>
       <c r="G19" s="17">
-        <v>5064</v>
+        <v>6545</v>
       </c>
       <c r="H19" s="17">
-        <v>7391</v>
+        <v>8160.71</v>
       </c>
       <c r="I19" s="17">
-        <v>8117</v>
+        <v>11883.57</v>
       </c>
       <c r="J19" s="17">
-        <v>7904</v>
+        <v>9752.14</v>
       </c>
       <c r="K19" s="17">
-        <v>4551</v>
+        <v>4953.57</v>
       </c>
       <c r="L19" s="17">
         <v>0</v>
       </c>
       <c r="M19" s="17">
-        <v>10957</v>
+        <v>15090.71</v>
       </c>
       <c r="N19" s="17">
-        <v>10744</v>
+        <v>12959.29</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="B24" s="18">
         <f t="shared" si="4"/>
-        <v>23375.760000000002</v>
+        <v>25557.919999999998</v>
       </c>
       <c r="C24" s="17">
         <v>1001</v>
@@ -2246,34 +2246,34 @@
         <v>341</v>
       </c>
       <c r="E24" s="17">
-        <v>1661.68</v>
+        <v>1522.71</v>
       </c>
       <c r="F24" s="17">
-        <v>2094.54</v>
+        <v>2691.93</v>
       </c>
       <c r="G24" s="17">
-        <v>1424.2</v>
+        <v>1566</v>
       </c>
       <c r="H24" s="17">
-        <v>2397.89</v>
+        <v>2313.4299999999998</v>
       </c>
       <c r="I24" s="17">
-        <v>2879.76</v>
+        <v>3531.64</v>
       </c>
       <c r="J24" s="17">
-        <v>2540.41</v>
+        <v>2736.71</v>
       </c>
       <c r="K24" s="17">
-        <v>1281.68</v>
+        <v>1142.71</v>
       </c>
       <c r="L24" s="17">
         <v>101</v>
       </c>
       <c r="M24" s="17">
-        <v>3995.97</v>
+        <v>4702.3599999999997</v>
       </c>
       <c r="N24" s="17">
-        <v>3656.63</v>
+        <v>3907.43</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="B25" s="18">
         <f t="shared" si="4"/>
-        <v>24742.17</v>
+        <v>28727.68</v>
       </c>
       <c r="C25" s="17">
         <v>3050</v>
@@ -2291,34 +2291,34 @@
         <v>50</v>
       </c>
       <c r="E25" s="17">
-        <v>888.71</v>
+        <v>715.71</v>
       </c>
       <c r="F25" s="17">
-        <v>2053.4299999999998</v>
+        <v>2793.93</v>
       </c>
       <c r="G25" s="17">
-        <v>1330.25</v>
+        <v>1466.25</v>
       </c>
       <c r="H25" s="17">
-        <v>2142.29</v>
+        <v>2237.14</v>
       </c>
       <c r="I25" s="17">
-        <v>3307</v>
+        <v>4315.3599999999997</v>
       </c>
       <c r="J25" s="17">
-        <v>2583.8200000000002</v>
+        <v>2987.68</v>
       </c>
       <c r="K25" s="17">
-        <v>888.71</v>
+        <v>715.71</v>
       </c>
       <c r="L25" s="17">
         <v>50</v>
       </c>
       <c r="M25" s="17">
-        <v>4560.57</v>
+        <v>5836.79</v>
       </c>
       <c r="N25" s="17">
-        <v>3837.39</v>
+        <v>4509.1099999999997</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="B26" s="19">
         <f t="shared" si="4"/>
-        <v>188950.93</v>
+        <v>213537.59000000003</v>
       </c>
       <c r="C26" s="19">
         <f t="shared" ref="C26:N26" si="5">SUM(C17:C25)</f>
@@ -2339,31 +2339,31 @@
       </c>
       <c r="E26" s="19">
         <f t="shared" si="5"/>
-        <v>12011.39</v>
+        <v>12101.989999999998</v>
       </c>
       <c r="F26" s="19">
         <f t="shared" si="5"/>
-        <v>17839.97</v>
+        <v>22577.29</v>
       </c>
       <c r="G26" s="19">
         <f t="shared" si="5"/>
-        <v>11878.45</v>
+        <v>13637.25</v>
       </c>
       <c r="H26" s="19">
         <f t="shared" si="5"/>
-        <v>18741.18</v>
+        <v>19521.28</v>
       </c>
       <c r="I26" s="19">
         <f t="shared" si="5"/>
-        <v>24863.760000000002</v>
+        <v>30290.57</v>
       </c>
       <c r="J26" s="19">
         <f t="shared" si="5"/>
-        <v>20888.23</v>
+        <v>23336.53</v>
       </c>
       <c r="K26" s="19">
         <f t="shared" si="5"/>
-        <v>9731.39</v>
+        <v>9821.989999999998</v>
       </c>
       <c r="L26" s="19">
         <f t="shared" si="5"/>
@@ -2371,11 +2371,11 @@
       </c>
       <c r="M26" s="19">
         <f t="shared" si="5"/>
-        <v>33873.54</v>
+        <v>39989.86</v>
       </c>
       <c r="N26" s="19">
         <f t="shared" si="5"/>
-        <v>29898.02</v>
+        <v>33035.83</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="B28" s="19">
         <f>SUM(C28:N28)</f>
-        <v>-45360.930000000008</v>
+        <v>18462.410000000003</v>
       </c>
       <c r="C28" s="19">
         <f t="shared" ref="C28:N28" si="6">C15-C26</f>
@@ -2414,31 +2414,31 @@
       </c>
       <c r="E28" s="19">
         <f t="shared" si="6"/>
-        <v>-6501.3899999999994</v>
+        <v>-501.98999999999796</v>
       </c>
       <c r="F28" s="19">
         <f t="shared" si="6"/>
-        <v>-6799.9700000000012</v>
+        <v>-1877.2900000000009</v>
       </c>
       <c r="G28" s="19">
         <f t="shared" si="6"/>
-        <v>-3898.4500000000007</v>
+        <v>1062.75</v>
       </c>
       <c r="H28" s="19">
         <f t="shared" si="6"/>
-        <v>-4231.18</v>
+        <v>4078.7200000000012</v>
       </c>
       <c r="I28" s="19">
         <f t="shared" si="6"/>
-        <v>-4823.760000000002</v>
+        <v>2409.4300000000003</v>
       </c>
       <c r="J28" s="19">
         <f t="shared" si="6"/>
-        <v>-3908.2299999999996</v>
+        <v>3363.4700000000012</v>
       </c>
       <c r="K28" s="19">
         <f t="shared" si="6"/>
-        <v>-4221.3899999999994</v>
+        <v>1778.010000000002</v>
       </c>
       <c r="L28" s="19">
         <f t="shared" si="6"/>
@@ -2446,11 +2446,11 @@
       </c>
       <c r="M28" s="19">
         <f t="shared" si="6"/>
-        <v>-4833.5400000000009</v>
+        <v>4710.1399999999994</v>
       </c>
       <c r="N28" s="19">
         <f t="shared" si="6"/>
-        <v>-3918.0200000000004</v>
+        <v>5664.1699999999983</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="B29" s="19">
         <f>N29</f>
-        <v>-45360.930000000008</v>
+        <v>18462.410000000003</v>
       </c>
       <c r="C29" s="19">
         <f t="shared" ref="C29:N29" si="7">C7+C28</f>
@@ -2471,43 +2471,43 @@
       </c>
       <c r="E29" s="19">
         <f t="shared" si="7"/>
-        <v>-8015.3899999999994</v>
+        <v>-2015.989999999998</v>
       </c>
       <c r="F29" s="19">
         <f t="shared" si="7"/>
-        <v>-14815.36</v>
+        <v>-3893.2799999999988</v>
       </c>
       <c r="G29" s="19">
         <f t="shared" si="7"/>
-        <v>-18713.810000000001</v>
+        <v>-2830.5299999999988</v>
       </c>
       <c r="H29" s="19">
         <f t="shared" si="7"/>
-        <v>-22944.99</v>
+        <v>1248.1900000000023</v>
       </c>
       <c r="I29" s="19">
         <f t="shared" si="7"/>
-        <v>-27768.750000000004</v>
+        <v>3657.6200000000026</v>
       </c>
       <c r="J29" s="19">
         <f t="shared" si="7"/>
-        <v>-31676.980000000003</v>
+        <v>7021.0900000000038</v>
       </c>
       <c r="K29" s="19">
         <f t="shared" si="7"/>
-        <v>-35898.370000000003</v>
+        <v>8799.1000000000058</v>
       </c>
       <c r="L29" s="19">
         <f t="shared" si="7"/>
-        <v>-36609.370000000003</v>
+        <v>8088.1000000000058</v>
       </c>
       <c r="M29" s="19">
         <f t="shared" si="7"/>
-        <v>-41442.910000000003</v>
+        <v>12798.240000000005</v>
       </c>
       <c r="N29" s="19">
         <f t="shared" si="7"/>
-        <v>-45360.930000000008</v>
+        <v>18462.410000000003</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="B34" s="19">
         <f>SUM(C34:N34)</f>
-        <v>52360.929999999993</v>
+        <v>-11462.410000000003</v>
       </c>
       <c r="C34" s="19">
         <f t="shared" ref="C34:N34" si="9">C26-C9-C10-C14</f>
@@ -2634,31 +2634,31 @@
       </c>
       <c r="E34" s="19">
         <f t="shared" si="9"/>
-        <v>6501.3899999999994</v>
+        <v>501.98999999999796</v>
       </c>
       <c r="F34" s="19">
         <f t="shared" si="9"/>
-        <v>6799.9700000000012</v>
+        <v>1877.2900000000009</v>
       </c>
       <c r="G34" s="19">
         <f t="shared" si="9"/>
-        <v>3898.4500000000007</v>
+        <v>-1062.75</v>
       </c>
       <c r="H34" s="19">
         <f t="shared" si="9"/>
-        <v>4231.18</v>
+        <v>-4078.7200000000012</v>
       </c>
       <c r="I34" s="19">
         <f t="shared" si="9"/>
-        <v>4823.760000000002</v>
+        <v>-2409.4300000000003</v>
       </c>
       <c r="J34" s="19">
         <f t="shared" si="9"/>
-        <v>3908.2299999999996</v>
+        <v>-3363.4700000000012</v>
       </c>
       <c r="K34" s="19">
         <f t="shared" si="9"/>
-        <v>4221.3899999999994</v>
+        <v>-1778.010000000002</v>
       </c>
       <c r="L34" s="19">
         <f t="shared" si="9"/>
@@ -2666,11 +2666,11 @@
       </c>
       <c r="M34" s="19">
         <f t="shared" si="9"/>
-        <v>4833.5400000000009</v>
+        <v>-4710.1399999999994</v>
       </c>
       <c r="N34" s="19">
         <f t="shared" si="9"/>
-        <v>3918.0200000000004</v>
+        <v>-5664.1699999999983</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -2688,43 +2688,43 @@
       </c>
       <c r="E35" s="21">
         <f t="shared" si="10"/>
-        <v>-1.2328732778682712</v>
+        <v>-4.0159963345883503</v>
       </c>
       <c r="F35" s="21">
         <f t="shared" si="10"/>
-        <v>-2.1787390238486344</v>
+        <v>-2.073883097443654</v>
       </c>
       <c r="G35" s="21">
         <f t="shared" si="10"/>
-        <v>-4.8003206402544594</v>
+        <v>0</v>
       </c>
       <c r="H35" s="21">
         <f t="shared" si="10"/>
-        <v>-5.4228347647701112</v>
+        <v>0</v>
       </c>
       <c r="I35" s="21">
         <f t="shared" si="10"/>
-        <v>-5.7566607791432389</v>
+        <v>0</v>
       </c>
       <c r="J35" s="21">
         <f t="shared" si="10"/>
-        <v>-8.105198516975717</v>
+        <v>0</v>
       </c>
       <c r="K35" s="21">
         <f t="shared" si="10"/>
-        <v>-8.5039216940391693</v>
+        <v>0</v>
       </c>
       <c r="L35" s="21">
         <f t="shared" si="10"/>
-        <v>-51.489971870604784</v>
+        <v>11.375668073136437</v>
       </c>
       <c r="M35" s="21">
         <f t="shared" si="10"/>
-        <v>-8.5740285587788652</v>
+        <v>0</v>
       </c>
       <c r="N35" s="21">
         <f t="shared" si="10"/>
-        <v>-11.577513642094733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="13" x14ac:dyDescent="0.3">
@@ -2807,7 +2807,7 @@
         <v>87</v>
       </c>
       <c r="B8" s="27">
-        <v>4363</v>
+        <v>2321</v>
       </c>
       <c r="C8" s="28" t="s">
         <v>101</v>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="B9" s="26">
         <f>IFERROR(AVERAGEIF('Suivi mensuel'!C34:N34,"&gt;0"),0)</f>
-        <v>4363.4108333333324</v>
+        <v>2320.8559999999998</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>89</v>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B10" s="29">
         <f>IF(B8&gt;0,B6/B8,0)</f>
-        <v>1.6044006417602568</v>
+        <v>3.015941404566997</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>90</v>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="B11" s="30">
         <f>IF(AND(B10&gt;0,B5&gt;0),EDATE(B5,INT(B10)),"")</f>
-        <v>46357</v>
+        <v>46419</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>92</v>
